--- a/dados/excel/genero_faixa_salarial.xlsx
+++ b/dados/excel/genero_faixa_salarial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$D$16</definedName>
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_faixa_salarial.xlsx
+++ b/dados/excel/genero_faixa_salarial.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>5986</v>
+        <v>5958</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>13265.64020307112</v>
+        <v>13262.95618159947</v>
       </c>
     </row>
     <row r="3">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>2428</v>
+        <v>2413</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>13837.8534083166</v>
+        <v>13838.74688805157</v>
       </c>
     </row>
     <row r="4">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>13213.87155107779</v>
+        <v>13373.73857874957</v>
       </c>
     </row>
     <row r="5">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>13809</v>
+        <v>13730</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>3437.034764703184</v>
+        <v>3436.792758811731</v>
       </c>
     </row>
     <row r="6">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>3623</v>
+        <v>3593</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>3683.0381719302</v>
+        <v>3684.749555517271</v>
       </c>
     </row>
     <row r="7">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>3533.918714555766</v>
+        <v>3509.624845843079</v>
       </c>
     </row>
     <row r="8">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>9502</v>
+        <v>9452</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>7326.522281993173</v>
+        <v>7328.410742673301</v>
       </c>
     </row>
     <row r="9">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3459</v>
+        <v>3437</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>7176.597027394431</v>
+        <v>7174.854114410678</v>
       </c>
     </row>
     <row r="10">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>7287.832346850733</v>
+        <v>7236.184078293289</v>
       </c>
     </row>
     <row r="11">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>2766</v>
+        <v>2752</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>28615.92434583663</v>
+        <v>28629.34342935216</v>
       </c>
     </row>
     <row r="12">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1611</v>
+        <v>1601</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>31056.95119406486</v>
+        <v>31073.24977777778</v>
       </c>
     </row>
     <row r="13">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>32673.70765232975</v>
+        <v>31131.24011538461</v>
       </c>
     </row>
     <row r="14">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>18966</v>
+        <v>18858</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>828.105700890703</v>
+        <v>827.9587525309115</v>
       </c>
     </row>
     <row r="15">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>4606</v>
+        <v>4567</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>807.2713322009222</v>
+        <v>806.5065941065303</v>
       </c>
     </row>
     <row r="16">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>285</v>
+        <v>432</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>772.797412721186</v>
+        <v>803.3515868936717</v>
       </c>
     </row>
   </sheetData>
